--- a/data_kuesioner.xlsx
+++ b/data_kuesioner.xlsx
@@ -8,23 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a0cf616d25d2132/Documents/pemodelan dan simulasi/modsim-2026-p2-ifs25026-latihan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{B3B88DDA-EB85-4A46-8BB2-2B422C0D7FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB2C325F-1FEB-4CE5-A04F-C0ABF11E43B4}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B3B88DDA-EB85-4A46-8BB2-2B422C0D7FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B43C7BB-473B-458A-9CA6-5D2203BB297D}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kuesioner" sheetId="1" r:id="rId1"/>
     <sheet name="Keterangan" sheetId="3" r:id="rId2"/>
     <sheet name="Pertanyaan" sheetId="2" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Kuesioner!$M$114</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Kuesioner!$M$2:$M$113</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Kuesioner!$M$114</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Kuesioner!$M$2:$M$113</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="/A36zV1Vv6cFqOSU9h3aHm73bNGIUXjyDhEctTwOPco="/>
     </ext>
@@ -297,6 +300,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
